--- a/assessment_forms/018_knowledge_assessment_for_seniors--assessment_forms.xlsx
+++ b/assessment_forms/018_knowledge_assessment_for_seniors--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,10 +440,10 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_question</t>
+          <t>physical_health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_question</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>How would you rate your overall health?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please select one of the options below.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,41 +547,49 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>first_question</t>
+          <t>mental_health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>first_question</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>How would you rate your mental health?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please select one of the options below.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>first_question</t>
+          <t>medication</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>first_question</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Do you take any prescription medication?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please answer "Yes" or "No".</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,41 +601,49 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>second_question</t>
+          <t>daily_activity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>second_question</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Are you able to perform daily activities like bathing, dressing, and cooking?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please answer "Yes" or "No".</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>second_question</t>
+          <t>social_support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>second_question</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>How much support do you have from family and friends?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please select one of the options below.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +655,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>third_question</t>
+          <t>memory_function</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>third_question</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>How would you rate your memory function?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please select one of the options below.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +682,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>third_question</t>
+          <t>cognitive_status</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>third_question</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Are you experiencing any cognitive decline?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please answer "Yes" or "No".</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fourth_question</t>
+          <t>hearing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fourth_question</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Do you have difficulty hearing?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please answer "Yes" or "No".</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fourth_question</t>
+          <t>vision</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fourth_question</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Do you have difficulty seeing?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please answer "Yes" or "No".</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,20 +758,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fifth_question</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fifth_question</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Additional notes</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please provide any additional comments or concerns.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -753,12 +793,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -781,340 +821,425 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>physical_health_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>physical_health_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>physical_health_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>physical_health_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>mental_health_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>first_question_choices</t>
+          <t>mental_health_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>second_question_choices</t>
+          <t>mental_health_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>second_question_choices</t>
+          <t>mental_health_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>second_question_choices</t>
+          <t>daily_activity_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>second_question_choices</t>
+          <t>daily_activity_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>social_support_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>family_members_often_visit_me</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Family members often visit me</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>social_support_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>i_visit_family_members_often</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>I visit family members often</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>social_support_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>friends_often_visit_me</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Friends often visit me</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>third_question_choices</t>
+          <t>social_support_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>i_visit_friends_often</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>I visit friends often</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fourth_question_choices</t>
+          <t>social_support_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fourth_question_choices</t>
+          <t>memory_function_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fourth_question_choices</t>
+          <t>memory_function_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fourth_question_choices</t>
+          <t>memory_function_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fifth_question_choices</t>
+          <t>memory_function_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fifth_question_choices</t>
+          <t>cognitive_status_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cognitive_status_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>hearing_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>hearing_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>vision_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>vision_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
